--- a/data/wettkaempfe.xlsx
+++ b/data/wettkaempfe.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA25DD7-6131-4ED0-AE0B-D762AE37EBB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F325E8-8AEA-41AC-A360-09D78FC4A4BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="wettkaempfe" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="121">
   <si>
     <t>Anlass</t>
   </si>
@@ -387,6 +387,15 @@
   </si>
   <si>
     <t>Heiss</t>
+  </si>
+  <si>
+    <t>Sustenderby</t>
+  </si>
+  <si>
+    <t>Skitour</t>
+  </si>
+  <si>
+    <t>1:16:21.0</t>
   </si>
 </sst>
 </file>
@@ -1221,26 +1230,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O62"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O63"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="40.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.81640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.26953125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="49.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="49.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1287,7 +1296,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -1322,7 +1331,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -1360,7 +1369,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1401,7 +1410,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -1445,7 +1454,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -1489,7 +1498,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -1530,7 +1539,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -1574,7 +1583,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -1618,7 +1627,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -1662,7 +1671,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -1706,7 +1715,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -1750,7 +1759,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1794,7 +1803,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -1838,7 +1847,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -1882,7 +1891,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -1926,7 +1935,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -1970,7 +1979,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -2014,7 +2023,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -2058,7 +2067,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -2105,7 +2114,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -2152,7 +2161,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -2196,7 +2205,7 @@
         <v>76.400000000000006</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -2216,7 +2225,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -2260,7 +2269,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -2304,7 +2313,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -2324,7 +2333,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>51</v>
       </c>
@@ -2365,7 +2374,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>51</v>
       </c>
@@ -2406,7 +2415,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>56</v>
       </c>
@@ -2444,7 +2453,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>56</v>
       </c>
@@ -2485,7 +2494,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>56</v>
       </c>
@@ -2526,7 +2535,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>56</v>
       </c>
@@ -2567,7 +2576,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>56</v>
       </c>
@@ -2611,7 +2620,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>56</v>
       </c>
@@ -2655,7 +2664,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>56</v>
       </c>
@@ -2699,7 +2708,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>67</v>
       </c>
@@ -2737,7 +2746,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>67</v>
       </c>
@@ -2778,7 +2787,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>67</v>
       </c>
@@ -2819,7 +2828,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>72</v>
       </c>
@@ -2860,7 +2869,7 @@
         <v>77.099999999999994</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>74</v>
       </c>
@@ -2901,7 +2910,7 @@
         <v>76.3</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>76</v>
       </c>
@@ -2939,7 +2948,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>78</v>
       </c>
@@ -2980,7 +2989,7 @@
         <v>4123</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>78</v>
       </c>
@@ -3024,7 +3033,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>78</v>
       </c>
@@ -3068,7 +3077,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>78</v>
       </c>
@@ -3109,7 +3118,7 @@
         <v>4243</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>78</v>
       </c>
@@ -3156,7 +3165,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>78</v>
       </c>
@@ -3203,7 +3212,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>78</v>
       </c>
@@ -3247,7 +3256,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>78</v>
       </c>
@@ -3291,7 +3300,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>78</v>
       </c>
@@ -3332,7 +3341,7 @@
         <v>77.8</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>89</v>
       </c>
@@ -3361,7 +3370,7 @@
         <v>76.5</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>89</v>
       </c>
@@ -3384,7 +3393,7 @@
         <v>75.400000000000006</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>91</v>
       </c>
@@ -3425,7 +3434,7 @@
         <v>76.5</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>93</v>
       </c>
@@ -3466,7 +3475,7 @@
         <v>3239</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>95</v>
       </c>
@@ -3504,7 +3513,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>98</v>
       </c>
@@ -3539,7 +3548,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>101</v>
       </c>
@@ -3556,7 +3565,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>102</v>
       </c>
@@ -3573,7 +3582,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>102</v>
       </c>
@@ -3590,7 +3599,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>102</v>
       </c>
@@ -3607,7 +3616,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>103</v>
       </c>
@@ -3648,7 +3657,7 @@
         <v>76.7</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>114</v>
       </c>
@@ -3693,6 +3702,35 @@
       </c>
       <c r="O62" t="s">
         <v>117</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>118</v>
+      </c>
+      <c r="B63" t="s">
+        <v>119</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>2026</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J63">
+        <v>3</v>
+      </c>
+      <c r="K63">
+        <v>15</v>
+      </c>
+      <c r="N63">
+        <v>82.4</v>
       </c>
     </row>
   </sheetData>

--- a/data/wettkaempfe.xlsx
+++ b/data/wettkaempfe.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F325E8-8AEA-41AC-A360-09D78FC4A4BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45848374-6561-4E2E-AB19-8A004CC5B2F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="wettkaempfe" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="124">
   <si>
     <t>Anlass</t>
   </si>
@@ -396,6 +396,15 @@
   </si>
   <si>
     <t>1:16:21.0</t>
+  </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
+    <t>1:08:07.0</t>
+  </si>
+  <si>
+    <t>Warm</t>
   </si>
 </sst>
 </file>
@@ -1230,26 +1239,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O63"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:O64"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.26953125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="49.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="49.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1296,7 +1305,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -1331,7 +1340,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -1369,7 +1378,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1410,7 +1419,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -1454,7 +1463,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -1498,7 +1507,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -1539,7 +1548,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -1583,7 +1592,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -1627,7 +1636,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -1671,7 +1680,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -1715,7 +1724,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -1759,7 +1768,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1803,7 +1812,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -1847,7 +1856,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -1891,7 +1900,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -1935,7 +1944,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -1979,7 +1988,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -2023,7 +2032,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -2067,7 +2076,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -2114,7 +2123,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -2161,7 +2170,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -2205,7 +2214,7 @@
         <v>76.400000000000006</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -2225,7 +2234,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -2269,7 +2278,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -2313,7 +2322,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -2333,7 +2342,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>51</v>
       </c>
@@ -2374,7 +2383,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>51</v>
       </c>
@@ -2415,7 +2424,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>56</v>
       </c>
@@ -2453,7 +2462,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>56</v>
       </c>
@@ -2494,7 +2503,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>56</v>
       </c>
@@ -2535,7 +2544,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>56</v>
       </c>
@@ -2576,7 +2585,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>56</v>
       </c>
@@ -2620,7 +2629,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>56</v>
       </c>
@@ -2664,7 +2673,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>56</v>
       </c>
@@ -2708,7 +2717,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>67</v>
       </c>
@@ -2746,7 +2755,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>67</v>
       </c>
@@ -2787,7 +2796,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>67</v>
       </c>
@@ -2828,7 +2837,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>72</v>
       </c>
@@ -2869,7 +2878,7 @@
         <v>77.099999999999994</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>74</v>
       </c>
@@ -2910,7 +2919,7 @@
         <v>76.3</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>76</v>
       </c>
@@ -2948,7 +2957,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>78</v>
       </c>
@@ -2989,7 +2998,7 @@
         <v>4123</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>78</v>
       </c>
@@ -3033,7 +3042,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>78</v>
       </c>
@@ -3077,7 +3086,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>78</v>
       </c>
@@ -3118,7 +3127,7 @@
         <v>4243</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>78</v>
       </c>
@@ -3165,7 +3174,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>78</v>
       </c>
@@ -3212,7 +3221,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>78</v>
       </c>
@@ -3256,7 +3265,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>78</v>
       </c>
@@ -3300,7 +3309,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>78</v>
       </c>
@@ -3341,7 +3350,7 @@
         <v>77.8</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>89</v>
       </c>
@@ -3370,7 +3379,7 @@
         <v>76.5</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>89</v>
       </c>
@@ -3393,7 +3402,7 @@
         <v>75.400000000000006</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>91</v>
       </c>
@@ -3434,7 +3443,7 @@
         <v>76.5</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>93</v>
       </c>
@@ -3475,7 +3484,7 @@
         <v>3239</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>95</v>
       </c>
@@ -3513,7 +3522,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>98</v>
       </c>
@@ -3548,7 +3557,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>101</v>
       </c>
@@ -3565,7 +3574,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>102</v>
       </c>
@@ -3582,7 +3591,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>102</v>
       </c>
@@ -3599,7 +3608,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>102</v>
       </c>
@@ -3616,7 +3625,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>103</v>
       </c>
@@ -3657,7 +3666,7 @@
         <v>76.7</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>114</v>
       </c>
@@ -3704,7 +3713,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>118</v>
       </c>
@@ -3731,6 +3740,53 @@
       </c>
       <c r="N63">
         <v>82.4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>114</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64">
+        <v>8550</v>
+      </c>
+      <c r="F64">
+        <v>2026</v>
+      </c>
+      <c r="G64">
+        <v>276</v>
+      </c>
+      <c r="H64" t="s">
+        <v>121</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J64">
+        <v>14</v>
+      </c>
+      <c r="K64">
+        <v>60</v>
+      </c>
+      <c r="L64">
+        <v>68</v>
+      </c>
+      <c r="M64">
+        <v>372</v>
+      </c>
+      <c r="N64">
+        <v>82.2</v>
+      </c>
+      <c r="O64" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
